--- a/files/SM1/K3/K3-P61P62-Weather.xlsx
+++ b/files/SM1/K3/K3-P61P62-Weather.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\finnish-space\files\SM1\K3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4352879C-FC90-4274-A40C-485EC394E5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A2569B-174D-448B-9A04-ED66634746CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="17720" windowHeight="10090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8430" yWindow="2540" windowWidth="17720" windowHeight="10090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>sää</t>
   </si>
@@ -186,6 +186,38 @@
   </si>
   <si>
     <t>outside</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selkeä</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salama</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salamoida</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lighten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jyristä</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thunder, rumble, boom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -535,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -762,6 +794,38 @@
         <v>54</v>
       </c>
     </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
